--- a/public/stocks.xlsx
+++ b/public/stocks.xlsx
@@ -4,8 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Stocks" sheetId="1" r:id="rId1"/>
-    <sheet name="IpoRights" sheetId="2" r:id="rId2"/>
-    <sheet name="SupportHistory" sheetId="3" r:id="rId3"/>
+    <sheet name="SupportHistory" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -377,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L249"/>
+  <dimension ref="A1:K247"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,9 +412,6 @@
       <c r="K1" t="str">
         <v>stoplossPrice</v>
       </c>
-      <c r="L1" t="str">
-        <v>addedAt</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -425,7 +421,7 @@
         <v>3000</v>
       </c>
       <c r="C2">
-        <v>2381.7410188984763</v>
+        <v>2418.974527222976</v>
       </c>
       <c r="D2">
         <v>1982.2649352752774</v>
@@ -440,16 +436,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2273.5</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K2">
-        <v>1932.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +447,10 @@
         <v>2563.9076098520663</v>
       </c>
       <c r="C3">
-        <v>2059.7966540820335</v>
+        <v>1920</v>
       </c>
       <c r="D3">
-        <v>1344</v>
+        <v>1487.7628536596771</v>
       </c>
       <c r="E3">
         <v>4200</v>
@@ -483,10 +470,10 @@
         <v>SMB</v>
       </c>
       <c r="B4">
-        <v>2249.4806641204573</v>
+        <v>2550</v>
       </c>
       <c r="C4">
-        <v>1728.2687236745367</v>
+        <v>1726.227445848278</v>
       </c>
       <c r="D4">
         <v>1428</v>
@@ -512,7 +499,7 @@
         <v>2500</v>
       </c>
       <c r="C5">
-        <v>1978.367660095618</v>
+        <v>1771.2900055556893</v>
       </c>
       <c r="D5">
         <v>1400</v>
@@ -535,10 +522,10 @@
         <v>MLBS</v>
       </c>
       <c r="B6">
-        <v>1439.8543494200653</v>
+        <v>1412.0322730766632</v>
       </c>
       <c r="C6">
-        <v>1328.528464611242</v>
+        <v>1156.932085306179</v>
       </c>
       <c r="D6">
         <v>854.56</v>
@@ -553,16 +540,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1623.8</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K6">
-        <v>1380.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -570,10 +548,10 @@
         <v>SHLB</v>
       </c>
       <c r="B7">
-        <v>1811.604536106445</v>
+        <v>1777.318099867861</v>
       </c>
       <c r="C7">
-        <v>1376</v>
+        <v>1375.257643406999</v>
       </c>
       <c r="D7">
         <v>963.2</v>
@@ -588,16 +566,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>2045</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K7">
-        <v>1675.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +574,7 @@
         <v>DLBS</v>
       </c>
       <c r="B8">
-        <v>1397.6577843731818</v>
+        <v>1287.1835454152301</v>
       </c>
       <c r="C8">
         <v>987.0890136202269</v>
@@ -631,7 +600,7 @@
         <v>SMFBS</v>
       </c>
       <c r="B9">
-        <v>1585.844369049101</v>
+        <v>1454.4270016373005</v>
       </c>
       <c r="C9">
         <v>1120</v>
@@ -657,7 +626,7 @@
         <v>GMFBS</v>
       </c>
       <c r="B10">
-        <v>1525.1132127692938</v>
+        <v>1487.3665579801868</v>
       </c>
       <c r="C10">
         <v>1208.019409357554</v>
@@ -675,16 +644,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1642</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K10">
-        <v>1395.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -695,7 +655,7 @@
         <v>1800</v>
       </c>
       <c r="C11">
-        <v>1300.5039955119314</v>
+        <v>1279.6306889307757</v>
       </c>
       <c r="D11">
         <v>1008</v>
@@ -710,16 +670,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1517.5</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K11">
-        <v>1140.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -727,7 +678,7 @@
         <v>UNLB</v>
       </c>
       <c r="B12">
-        <v>2189.64948564586</v>
+        <v>1940.878057750344</v>
       </c>
       <c r="C12">
         <v>1580.5978358128787</v>
@@ -745,16 +696,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>2277.9</v>
-      </c>
-      <c r="J12" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K12">
-        <v>1936.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +704,7 @@
         <v>USLB</v>
       </c>
       <c r="B13">
-        <v>1786.3847687049931</v>
+        <v>1628.2002085370848</v>
       </c>
       <c r="C13">
         <v>1072</v>
@@ -788,10 +730,10 @@
         <v>JSLBB</v>
       </c>
       <c r="B14">
-        <v>1369.7206440300556</v>
+        <v>1450</v>
       </c>
       <c r="C14">
-        <v>1280.8062436213104</v>
+        <v>1271.0811327510523</v>
       </c>
       <c r="D14">
         <v>812</v>
@@ -817,7 +759,7 @@
         <v>1950</v>
       </c>
       <c r="C15">
-        <v>1643.6668875697364</v>
+        <v>1729.488284043348</v>
       </c>
       <c r="D15">
         <v>1064</v>
@@ -840,7 +782,7 @@
         <v>CYCL</v>
       </c>
       <c r="B16">
-        <v>1562.2546614338494</v>
+        <v>1526.006636568069</v>
       </c>
       <c r="C16">
         <v>1120</v>
@@ -858,16 +800,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1689</v>
-      </c>
-      <c r="J16" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K16">
-        <v>1435.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -875,7 +808,7 @@
         <v>MLBSL</v>
       </c>
       <c r="B17">
-        <v>2074.2447902494023</v>
+        <v>2026.7965272383099</v>
       </c>
       <c r="C17">
         <v>1520</v>
@@ -901,7 +834,7 @@
         <v>MLBBL</v>
       </c>
       <c r="B18">
-        <v>1453.724251215561</v>
+        <v>1439.4946003222888</v>
       </c>
       <c r="C18">
         <v>994.5473542155197</v>
@@ -927,7 +860,7 @@
         <v>MSLB</v>
       </c>
       <c r="B19">
-        <v>1328.1255879656374</v>
+        <v>1337.7840475587948</v>
       </c>
       <c r="C19">
         <v>880</v>
@@ -953,7 +886,7 @@
         <v>AVYAN</v>
       </c>
       <c r="B20">
-        <v>970.4196629491734</v>
+        <v>913.3741889210999</v>
       </c>
       <c r="C20">
         <v>680</v>
@@ -979,7 +912,7 @@
         <v>LLBS</v>
       </c>
       <c r="B21">
-        <v>1069.6367778468489</v>
+        <v>1042.7577614793636</v>
       </c>
       <c r="C21">
         <v>866.9538333834621</v>
@@ -997,16 +930,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1040</v>
-      </c>
-      <c r="J21" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K21">
-        <v>884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1014,7 +938,7 @@
         <v>KMCDB</v>
       </c>
       <c r="B22">
-        <v>1013.1511089183986</v>
+        <v>987.500613031963</v>
       </c>
       <c r="C22">
         <v>768.2843192473887</v>
@@ -1032,16 +956,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1061</v>
-      </c>
-      <c r="J22" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K22">
-        <v>901.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1052,7 +967,7 @@
         <v>910</v>
       </c>
       <c r="C23">
-        <v>838.9398731008527</v>
+        <v>764.4072028014127</v>
       </c>
       <c r="D23">
         <v>509.6</v>
@@ -1067,16 +982,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
-      </c>
-      <c r="I23">
-        <v>825</v>
-      </c>
-      <c r="J23" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K23">
-        <v>701.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1084,7 +990,7 @@
         <v>ACLBSL</v>
       </c>
       <c r="B24">
-        <v>1014.4337455150155</v>
+        <v>963.8167402864678</v>
       </c>
       <c r="C24">
         <v>756.283178727095</v>
@@ -1110,7 +1016,7 @@
         <v>HLBSL</v>
       </c>
       <c r="B25">
-        <v>940.193576447119</v>
+        <v>930.2410939829131</v>
       </c>
       <c r="C25">
         <v>713.4826393616156</v>
@@ -1136,7 +1042,7 @@
         <v>ILBS</v>
       </c>
       <c r="B26">
-        <v>1010.1990594057785</v>
+        <v>1046.4684479332088</v>
       </c>
       <c r="C26">
         <v>798.505556618492</v>
@@ -1162,7 +1068,7 @@
         <v>SMATA</v>
       </c>
       <c r="B27">
-        <v>891.0909276280511</v>
+        <v>854.6886193456356</v>
       </c>
       <c r="C27">
         <v>653.4460266842731</v>
@@ -1188,7 +1094,7 @@
         <v>GILB</v>
       </c>
       <c r="B28">
-        <v>1229.1936589372865</v>
+        <v>1215.6685671484965</v>
       </c>
       <c r="C28">
         <v>966.8190261750462</v>
@@ -1214,7 +1120,7 @@
         <v>MATRI</v>
       </c>
       <c r="B29">
-        <v>1153.493126148536</v>
+        <v>1159.7283682546977</v>
       </c>
       <c r="C29">
         <v>920</v>
@@ -1240,7 +1146,7 @@
         <v>VLBS</v>
       </c>
       <c r="B30">
-        <v>831.9006494863378</v>
+        <v>823.8092170446541</v>
       </c>
       <c r="C30">
         <v>672.0882741365056</v>
@@ -1266,7 +1172,7 @@
         <v>SMPDA</v>
       </c>
       <c r="B31">
-        <v>924.1562069480592</v>
+        <v>889.403710188706</v>
       </c>
       <c r="C31">
         <v>720</v>
@@ -1292,7 +1198,7 @@
         <v>ALBSL</v>
       </c>
       <c r="B32">
-        <v>879.8801670665248</v>
+        <v>929.3160150760716</v>
       </c>
       <c r="C32">
         <v>624</v>
@@ -1318,7 +1224,7 @@
         <v>NMBMF</v>
       </c>
       <c r="B33">
-        <v>689.5769988553646</v>
+        <v>682.4807389331768</v>
       </c>
       <c r="C33">
         <v>536</v>
@@ -1344,7 +1250,7 @@
         <v>GBLBS</v>
       </c>
       <c r="B34">
-        <v>773.7141578396584</v>
+        <v>744.629402443228</v>
       </c>
       <c r="C34">
         <v>629.7738868844954</v>
@@ -1370,7 +1276,7 @@
         <v>SLBBL</v>
       </c>
       <c r="B35">
-        <v>901.1371346083879</v>
+        <v>862.0977264609891</v>
       </c>
       <c r="C35">
         <v>740.6948851845608</v>
@@ -1396,7 +1302,7 @@
         <v>NMFBS</v>
       </c>
       <c r="B36">
-        <v>1304.1883743544715</v>
+        <v>1242.2848129638983</v>
       </c>
       <c r="C36">
         <v>904</v>
@@ -1422,10 +1328,10 @@
         <v>FOWAD</v>
       </c>
       <c r="B37">
-        <v>1161.6246985411758</v>
+        <v>1200</v>
       </c>
       <c r="C37">
-        <v>1067.2068910148766</v>
+        <v>1072.072643387713</v>
       </c>
       <c r="D37">
         <v>672</v>
@@ -1448,7 +1354,7 @@
         <v>SWBBL</v>
       </c>
       <c r="B38">
-        <v>845.2862263341104</v>
+        <v>823.7626074591309</v>
       </c>
       <c r="C38">
         <v>774.274080017918</v>
@@ -1474,7 +1380,7 @@
         <v>RSDC</v>
       </c>
       <c r="B39">
-        <v>690.2227492030717</v>
+        <v>681.0544511396529</v>
       </c>
       <c r="C39">
         <v>585.3532040031477</v>
@@ -1500,7 +1406,7 @@
         <v>JBLB</v>
       </c>
       <c r="B40">
-        <v>1330.2560661332893</v>
+        <v>1330.695885884286</v>
       </c>
       <c r="C40">
         <v>1104</v>
@@ -1518,16 +1424,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
-      </c>
-      <c r="I40">
-        <v>1300</v>
-      </c>
-      <c r="J40" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K40">
-        <v>1105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1535,7 +1432,7 @@
         <v>MERO</v>
       </c>
       <c r="B41">
-        <v>748.0774121944426</v>
+        <v>711.0212217308268</v>
       </c>
       <c r="C41">
         <v>528</v>
@@ -1561,7 +1458,7 @@
         <v>SWMF</v>
       </c>
       <c r="B42">
-        <v>745.8699749915643</v>
+        <v>709.3808712496597</v>
       </c>
       <c r="C42">
         <v>655.5979097665286</v>
@@ -1587,10 +1484,10 @@
         <v>NICLBSL</v>
       </c>
       <c r="B43">
-        <v>651.3366310148687</v>
+        <v>654.3028526713279</v>
       </c>
       <c r="C43">
-        <v>504</v>
+        <v>573.3880142364068</v>
       </c>
       <c r="D43">
         <v>352.8</v>
@@ -1613,7 +1510,7 @@
         <v>FMDBL</v>
       </c>
       <c r="B44">
-        <v>768.7314863670482</v>
+        <v>727.6477703915748</v>
       </c>
       <c r="C44">
         <v>592</v>
@@ -1639,7 +1536,7 @@
         <v>NMLBBL</v>
       </c>
       <c r="B45">
-        <v>671.7991953073918</v>
+        <v>650.4451721095257</v>
       </c>
       <c r="C45">
         <v>496</v>
@@ -1657,16 +1554,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
-      </c>
-      <c r="I45">
-        <v>638</v>
-      </c>
-      <c r="J45" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K45">
-        <v>542.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1562,7 @@
         <v>DDBL</v>
       </c>
       <c r="B46">
-        <v>809.1419109247876</v>
+        <v>781.1853853888263</v>
       </c>
       <c r="C46">
         <v>600</v>
@@ -1700,7 +1588,7 @@
         <v>NUBL</v>
       </c>
       <c r="B47">
-        <v>688.9247212750771</v>
+        <v>688.6898920688988</v>
       </c>
       <c r="C47">
         <v>560</v>
@@ -1726,7 +1614,7 @@
         <v>SKBBL</v>
       </c>
       <c r="B48">
-        <v>839.6375633118708</v>
+        <v>797.2630451004485</v>
       </c>
       <c r="C48">
         <v>624</v>
@@ -1752,7 +1640,7 @@
         <v>ANLB</v>
       </c>
       <c r="B49">
-        <v>4977.488126783053</v>
+        <v>5101.634396410982</v>
       </c>
       <c r="C49">
         <v>3200</v>
@@ -1778,7 +1666,7 @@
         <v>ULBSL</v>
       </c>
       <c r="B50">
-        <v>3115.580892514336</v>
+        <v>3177.946067463954</v>
       </c>
       <c r="C50">
         <v>2257.1642038109544</v>
@@ -1804,7 +1692,7 @@
         <v>CBBL</v>
       </c>
       <c r="B51">
-        <v>914.2881601206557</v>
+        <v>899.9546906229294</v>
       </c>
       <c r="C51">
         <v>664</v>
@@ -1833,10 +1721,10 @@
         <v>2200</v>
       </c>
       <c r="C52">
-        <v>1494.0108618298216</v>
+        <v>1494.2395463726507</v>
       </c>
       <c r="D52">
-        <v>1232</v>
+        <v>1132.6815220553437</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -1859,7 +1747,7 @@
         <v>750</v>
       </c>
       <c r="C53">
-        <v>687.3664304883918</v>
+        <v>682.307315486079</v>
       </c>
       <c r="D53">
         <v>420</v>
@@ -1882,7 +1770,7 @@
         <v>SPL</v>
       </c>
       <c r="B54">
-        <v>851.5386293537421</v>
+        <v>684.7803684012969</v>
       </c>
       <c r="C54">
         <v>480</v>
@@ -1908,10 +1796,10 @@
         <v>BHPL</v>
       </c>
       <c r="B55">
-        <v>698.4583363545931</v>
+        <v>694.0604746480932</v>
       </c>
       <c r="C55">
-        <v>449.6</v>
+        <v>542.4946714395959</v>
       </c>
       <c r="D55">
         <v>314.72</v>
@@ -1934,10 +1822,10 @@
         <v>USHL</v>
       </c>
       <c r="B56">
-        <v>597.4112051149184</v>
+        <v>571.3852302813458</v>
       </c>
       <c r="C56">
-        <v>449.6</v>
+        <v>485.950872820594</v>
       </c>
       <c r="D56">
         <v>314.72</v>
@@ -1963,7 +1851,7 @@
         <v>535.2600145633729</v>
       </c>
       <c r="C57">
-        <v>447.19291673355673</v>
+        <v>436.40161314063977</v>
       </c>
       <c r="D57">
         <v>297.92</v>
@@ -1978,16 +1866,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="b">
-        <v>1</v>
-      </c>
-      <c r="I57">
-        <v>590</v>
-      </c>
-      <c r="J57" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K57">
-        <v>501.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1998,7 +1877,7 @@
         <v>623.3559454687883</v>
       </c>
       <c r="C58">
-        <v>484.1856841523595</v>
+        <v>473.3039923315543</v>
       </c>
       <c r="D58">
         <v>314.72</v>
@@ -2021,10 +1900,10 @@
         <v>TSHL</v>
       </c>
       <c r="B59">
-        <v>790.5660124065746</v>
+        <v>632.4919004802331</v>
       </c>
       <c r="C59">
-        <v>517.5004208642675</v>
+        <v>527.0351008767016</v>
       </c>
       <c r="D59">
         <v>336</v>
@@ -2047,7 +1926,7 @@
         <v>MSHL</v>
       </c>
       <c r="B60">
-        <v>680.969468875386</v>
+        <v>681.247820299856</v>
       </c>
       <c r="C60">
         <v>540</v>
@@ -2073,10 +1952,10 @@
         <v>RAWA</v>
       </c>
       <c r="B61">
-        <v>622.2058338727713</v>
+        <v>626.5592337981961</v>
       </c>
       <c r="C61">
-        <v>449.6</v>
+        <v>496.2067068566044</v>
       </c>
       <c r="D61">
         <v>314.72</v>
@@ -2102,7 +1981,7 @@
         <v>660.6819741196163</v>
       </c>
       <c r="C62">
-        <v>497.82667420869296</v>
+        <v>494.3830806202653</v>
       </c>
       <c r="D62">
         <v>252</v>
@@ -2125,7 +2004,7 @@
         <v>BGWT</v>
       </c>
       <c r="B63">
-        <v>712.0924716511169</v>
+        <v>679.1904900243388</v>
       </c>
       <c r="C63">
         <v>516.8</v>
@@ -2151,7 +2030,7 @@
         <v>CKHL</v>
       </c>
       <c r="B64">
-        <v>614.5306686286656</v>
+        <v>609.6336109859978</v>
       </c>
       <c r="C64">
         <v>372</v>
@@ -2177,7 +2056,7 @@
         <v>MCHL</v>
       </c>
       <c r="B65">
-        <v>475.54265966202206</v>
+        <v>399.13666287771485</v>
       </c>
       <c r="C65">
         <v>281.6</v>
@@ -2203,10 +2082,10 @@
         <v>SIKLES</v>
       </c>
       <c r="B66">
-        <v>828.311189898474</v>
+        <v>664.1775348518538</v>
       </c>
       <c r="C66">
-        <v>576</v>
+        <v>533.0063115951641</v>
       </c>
       <c r="D66">
         <v>403.20000000000005</v>
@@ -2232,7 +2111,7 @@
         <v>585</v>
       </c>
       <c r="C67">
-        <v>452.96856095017637</v>
+        <v>428.89466565382514</v>
       </c>
       <c r="D67">
         <v>327.6</v>
@@ -2255,7 +2134,7 @@
         <v>MANDU</v>
       </c>
       <c r="B68">
-        <v>854.415071153611</v>
+        <v>853.7609381643772</v>
       </c>
       <c r="C68">
         <v>492</v>
@@ -2281,7 +2160,7 @@
         <v>IHL</v>
       </c>
       <c r="B69">
-        <v>483.97560565301404</v>
+        <v>471.6723323454681</v>
       </c>
       <c r="C69">
         <v>240</v>
@@ -2307,10 +2186,10 @@
         <v>UHEWA</v>
       </c>
       <c r="B70">
-        <v>503.6365203296025</v>
+        <v>506.01800473269464</v>
       </c>
       <c r="C70">
-        <v>403.2</v>
+        <v>397.8625367745266</v>
       </c>
       <c r="D70">
         <v>282.24</v>
@@ -2333,10 +2212,10 @@
         <v>MKHL</v>
       </c>
       <c r="B71">
-        <v>833.5724827806571</v>
+        <v>603.6396506306322</v>
       </c>
       <c r="C71">
-        <v>372</v>
+        <v>445.027013237799</v>
       </c>
       <c r="D71">
         <v>260.4</v>
@@ -2359,7 +2238,7 @@
         <v>MMKJL</v>
       </c>
       <c r="B72">
-        <v>504.3924131699934</v>
+        <v>501.3055169930635</v>
       </c>
       <c r="C72">
         <v>396</v>
@@ -2385,10 +2264,10 @@
         <v>BEDC</v>
       </c>
       <c r="B73">
-        <v>555.810530862951</v>
+        <v>547.9352990206874</v>
       </c>
       <c r="C73">
-        <v>336</v>
+        <v>471.84304234803807</v>
       </c>
       <c r="D73">
         <v>235.2</v>
@@ -2411,10 +2290,10 @@
         <v>MAKAR</v>
       </c>
       <c r="B74">
-        <v>521.1030608090872</v>
+        <v>636.3315871604892</v>
       </c>
       <c r="C74">
-        <v>348</v>
+        <v>391.5790744304657</v>
       </c>
       <c r="D74">
         <v>243.60000000000002</v>
@@ -2437,7 +2316,7 @@
         <v>DOLTI</v>
       </c>
       <c r="B75">
-        <v>514.6513881884072</v>
+        <v>439.3513270388929</v>
       </c>
       <c r="C75">
         <v>360</v>
@@ -2455,16 +2334,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="b">
-        <v>1</v>
-      </c>
-      <c r="I75">
-        <v>590</v>
-      </c>
-      <c r="J75" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K75">
-        <v>501.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2472,7 +2342,7 @@
         <v>BHDC</v>
       </c>
       <c r="B76">
-        <v>528.4262864094189</v>
+        <v>522.1670598546073</v>
       </c>
       <c r="C76">
         <v>486.80391345507786</v>
@@ -2490,16 +2360,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="b">
-        <v>1</v>
-      </c>
-      <c r="I76">
-        <v>516</v>
-      </c>
-      <c r="J76" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K76">
-        <v>430.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2510,7 +2371,7 @@
         <v>569.8626343069329</v>
       </c>
       <c r="C77">
-        <v>506.1898064952316</v>
+        <v>493.387355084437</v>
       </c>
       <c r="D77">
         <v>336</v>
@@ -2536,7 +2397,7 @@
         <v>493.6683392467045</v>
       </c>
       <c r="C78">
-        <v>382.64659033951483</v>
+        <v>381.7072442568438</v>
       </c>
       <c r="D78">
         <v>220</v>
@@ -2559,7 +2420,7 @@
         <v>HHL</v>
       </c>
       <c r="B79">
-        <v>384.79152232973877</v>
+        <v>405.6075412131134</v>
       </c>
       <c r="C79">
         <v>256</v>
@@ -2574,19 +2435,10 @@
         <v>HYDROPOWER</v>
       </c>
       <c r="G79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="b">
-        <v>1</v>
-      </c>
-      <c r="I79">
-        <v>364</v>
-      </c>
-      <c r="J79" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K79">
-        <v>309.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2594,10 +2446,10 @@
         <v>SMHL</v>
       </c>
       <c r="B80">
-        <v>958.8610652386903</v>
+        <v>902.5209848631177</v>
       </c>
       <c r="C80">
-        <v>456</v>
+        <v>516.0511349532654</v>
       </c>
       <c r="D80">
         <v>319.20000000000005</v>
@@ -2623,10 +2475,10 @@
         <v>540</v>
       </c>
       <c r="C81">
-        <v>428.6299678587793</v>
+        <v>411.7260164897871</v>
       </c>
       <c r="D81">
-        <v>329.1431186760137</v>
+        <v>327.98756857897223</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2652,7 +2504,7 @@
         <v>296</v>
       </c>
       <c r="D82">
-        <v>242.83192224239292</v>
+        <v>229.6423949337241</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2664,16 +2516,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="b">
-        <v>1</v>
-      </c>
-      <c r="I82">
-        <v>408.4</v>
-      </c>
-      <c r="J82" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K82">
-        <v>286.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2681,7 +2524,7 @@
         <v>MKHC</v>
       </c>
       <c r="B83">
-        <v>382.1845261738133</v>
+        <v>349.9545403556951</v>
       </c>
       <c r="C83">
         <v>264</v>
@@ -2707,10 +2550,10 @@
         <v>SGHC</v>
       </c>
       <c r="B84">
-        <v>379.3995610143177</v>
+        <v>392.47873331290407</v>
       </c>
       <c r="C84">
-        <v>280</v>
+        <v>319.74866306737584</v>
       </c>
       <c r="D84">
         <v>196</v>
@@ -2725,16 +2568,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="b">
-        <v>1</v>
-      </c>
-      <c r="I84">
-        <v>472.2</v>
-      </c>
-      <c r="J84" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K84">
-        <v>355.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2742,10 +2576,10 @@
         <v>PPL</v>
       </c>
       <c r="B85">
-        <v>428.4779619683956</v>
+        <v>446.5840940072558</v>
       </c>
       <c r="C85">
-        <v>344</v>
+        <v>376.075</v>
       </c>
       <c r="D85">
         <v>240.8</v>
@@ -2768,7 +2602,7 @@
         <v>TVCL</v>
       </c>
       <c r="B86">
-        <v>459.59717775009193</v>
+        <v>463.85523321698724</v>
       </c>
       <c r="C86">
         <v>352</v>
@@ -2794,7 +2628,7 @@
         <v>MEHL</v>
       </c>
       <c r="B87">
-        <v>381.3487473427239</v>
+        <v>364.20984663022887</v>
       </c>
       <c r="C87">
         <v>320</v>
@@ -2820,7 +2654,7 @@
         <v>MHCL</v>
       </c>
       <c r="B88">
-        <v>410.5304084785104</v>
+        <v>390.3780199264378</v>
       </c>
       <c r="C88">
         <v>288</v>
@@ -2846,10 +2680,10 @@
         <v>RFPL</v>
       </c>
       <c r="B89">
-        <v>499.69914926781513</v>
+        <v>459.165803769248</v>
       </c>
       <c r="C89">
-        <v>280</v>
+        <v>343.23233980037173</v>
       </c>
       <c r="D89">
         <v>196</v>
@@ -2864,16 +2698,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="b">
-        <v>1</v>
-      </c>
-      <c r="I89">
-        <v>525</v>
-      </c>
-      <c r="J89" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K89">
-        <v>446.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2881,7 +2706,7 @@
         <v>GVL</v>
       </c>
       <c r="B90">
-        <v>500.314134425978</v>
+        <v>486.453057321528</v>
       </c>
       <c r="C90">
         <v>240</v>
@@ -2899,16 +2724,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
-      </c>
-      <c r="I90">
-        <v>438</v>
-      </c>
-      <c r="J90" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K90">
-        <v>400.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2919,7 +2735,7 @@
         <v>330.60952380952375</v>
       </c>
       <c r="C91">
-        <v>210.20332133137308</v>
+        <v>195</v>
       </c>
       <c r="D91">
         <v>112</v>
@@ -2934,16 +2750,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="b">
-        <v>1</v>
-      </c>
-      <c r="I91">
-        <v>223.7</v>
-      </c>
-      <c r="J91" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K91">
-        <v>190.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2951,7 +2758,7 @@
         <v>JOSHI</v>
       </c>
       <c r="B92">
-        <v>302.56523652525516</v>
+        <v>286.46233874166245</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -2969,16 +2776,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="b">
-        <v>1</v>
-      </c>
-      <c r="I92">
-        <v>333.9</v>
-      </c>
-      <c r="J92" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K92">
-        <v>283.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2986,7 +2784,7 @@
         <v>MKJC</v>
       </c>
       <c r="B93">
-        <v>516.1416079538136</v>
+        <v>519.1432624344144</v>
       </c>
       <c r="C93">
         <v>320</v>
@@ -3015,10 +2813,10 @@
         <v>363.61117991382713</v>
       </c>
       <c r="C94">
-        <v>276.9080740171388</v>
+        <v>309.2761634910831</v>
       </c>
       <c r="D94">
-        <v>212.8</v>
+        <v>235.57043490533312</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3030,16 +2828,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="b">
-        <v>1</v>
-      </c>
-      <c r="I94">
-        <v>311</v>
-      </c>
-      <c r="J94" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K94">
-        <v>264.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3047,10 +2836,10 @@
         <v>NHDL</v>
       </c>
       <c r="B95">
-        <v>616.0763936476967</v>
+        <v>596.0493211370036</v>
       </c>
       <c r="C95">
-        <v>320</v>
+        <v>422.979556120905</v>
       </c>
       <c r="D95">
         <v>224</v>
@@ -3073,7 +2862,7 @@
         <v>BNHC</v>
       </c>
       <c r="B96">
-        <v>481.1308952334565</v>
+        <v>476.38173169292384</v>
       </c>
       <c r="C96">
         <v>240</v>
@@ -3091,16 +2880,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="b">
-        <v>1</v>
-      </c>
-      <c r="I96">
-        <v>526.9</v>
-      </c>
-      <c r="J96" t="str">
-        <v>2025-07-25</v>
-      </c>
-      <c r="K96">
-        <v>443.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3111,7 +2891,7 @@
         <v>495.8513322165452</v>
       </c>
       <c r="C97">
-        <v>356.1070519361727</v>
+        <v>381.1</v>
       </c>
       <c r="D97">
         <v>224</v>
@@ -3126,16 +2906,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="b">
-        <v>1</v>
-      </c>
-      <c r="I97">
-        <v>364</v>
-      </c>
-      <c r="J97" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K97">
-        <v>309.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3146,7 +2917,7 @@
         <v>357.92684500711425</v>
       </c>
       <c r="C98">
-        <v>304.9567442773857</v>
+        <v>275</v>
       </c>
       <c r="D98">
         <v>190</v>
@@ -3161,16 +2932,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="b">
-        <v>1</v>
-      </c>
-      <c r="I98">
-        <v>390</v>
-      </c>
-      <c r="J98" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K98">
-        <v>280.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3178,7 +2940,7 @@
         <v>UMRH</v>
       </c>
       <c r="B99">
-        <v>528.3777579762191</v>
+        <v>503.99775353859656</v>
       </c>
       <c r="C99">
         <v>320</v>
@@ -3204,7 +2966,7 @@
         <v>SMJC</v>
       </c>
       <c r="B100">
-        <v>544.3689281992501</v>
+        <v>401.7732451326294</v>
       </c>
       <c r="C100">
         <v>272</v>
@@ -3236,7 +2998,7 @@
         <v>278.85903563874103</v>
       </c>
       <c r="D101">
-        <v>222.93527765371473</v>
+        <v>217.24547727335863</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3248,16 +3010,7 @@
         <v>0</v>
       </c>
       <c r="H101" t="b">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>200</v>
-      </c>
-      <c r="J101" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K101">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3265,7 +3018,7 @@
         <v>TAMOR</v>
       </c>
       <c r="B102">
-        <v>389.6608679419387</v>
+        <v>389.63952050433886</v>
       </c>
       <c r="C102">
         <v>320</v>
@@ -3291,7 +3044,7 @@
         <v>SPC</v>
       </c>
       <c r="B103">
-        <v>511.7583636142057</v>
+        <v>508.60143880012856</v>
       </c>
       <c r="C103">
         <v>266.4</v>
@@ -3309,16 +3062,7 @@
         <v>0</v>
       </c>
       <c r="H103" t="b">
-        <v>1</v>
-      </c>
-      <c r="I103">
-        <v>539</v>
-      </c>
-      <c r="J103" t="str">
-        <v>2025-07-25</v>
-      </c>
-      <c r="K103">
-        <v>450.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3329,7 +3073,7 @@
         <v>425.96328273483243</v>
       </c>
       <c r="C104">
-        <v>319.0570642002359</v>
+        <v>231.4802847012396</v>
       </c>
       <c r="D104">
         <v>168</v>
@@ -3352,10 +3096,10 @@
         <v>PHCL</v>
       </c>
       <c r="B105">
-        <v>417.09566630253124</v>
+        <v>428.0582063340357</v>
       </c>
       <c r="C105">
-        <v>360</v>
+        <v>324.74194825331165</v>
       </c>
       <c r="D105">
         <v>252</v>
@@ -3378,7 +3122,7 @@
         <v>RURU</v>
       </c>
       <c r="B106">
-        <v>684.3370731009527</v>
+        <v>680.4752718072439</v>
       </c>
       <c r="C106">
         <v>527.9158038625341</v>
@@ -3407,7 +3151,7 @@
         <v>300</v>
       </c>
       <c r="C107">
-        <v>224.63031902073456</v>
+        <v>222.54324477881514</v>
       </c>
       <c r="D107">
         <v>168</v>
@@ -3422,16 +3166,7 @@
         <v>0</v>
       </c>
       <c r="H107" t="b">
-        <v>1</v>
-      </c>
-      <c r="I107">
-        <v>311</v>
-      </c>
-      <c r="J107" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K107">
-        <v>264.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3439,7 +3174,7 @@
         <v>UNHPL</v>
       </c>
       <c r="B108">
-        <v>309.0786783522084</v>
+        <v>330.7068055631583</v>
       </c>
       <c r="C108">
         <v>208</v>
@@ -3465,7 +3200,7 @@
         <v>KPCL</v>
       </c>
       <c r="B109">
-        <v>519.1102993551968</v>
+        <v>482.51832438457984</v>
       </c>
       <c r="C109">
         <v>328</v>
@@ -3491,7 +3226,7 @@
         <v>PPCL</v>
       </c>
       <c r="B110">
-        <v>299.8175460517249</v>
+        <v>277.7699977362338</v>
       </c>
       <c r="C110">
         <v>240</v>
@@ -3509,16 +3244,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="b">
-        <v>1</v>
-      </c>
-      <c r="I110">
-        <v>350</v>
-      </c>
-      <c r="J110" t="str">
-        <v>2025-07-25T02:18:06.713Z</v>
-      </c>
-      <c r="K110">
-        <v>325.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3526,10 +3252,10 @@
         <v>HPPL</v>
       </c>
       <c r="B111">
-        <v>398.8533405966579</v>
+        <v>460.7243916261084</v>
       </c>
       <c r="C111">
-        <v>320</v>
+        <v>348.1596739106813</v>
       </c>
       <c r="D111">
         <v>224</v>
@@ -3552,7 +3278,7 @@
         <v>PMHPL</v>
       </c>
       <c r="B112">
-        <v>283.3451327643025</v>
+        <v>280.68973480265726</v>
       </c>
       <c r="C112">
         <v>170.4</v>
@@ -3578,10 +3304,10 @@
         <v>SPDL</v>
       </c>
       <c r="B113">
-        <v>340.94623843139647</v>
+        <v>326.8703572261941</v>
       </c>
       <c r="C113">
-        <v>176</v>
+        <v>245.82637208541615</v>
       </c>
       <c r="D113">
         <v>123.2</v>
@@ -3604,7 +3330,7 @@
         <v>UMHL</v>
       </c>
       <c r="B114">
-        <v>480.0048976789092</v>
+        <v>369.32055905759796</v>
       </c>
       <c r="C114">
         <v>256</v>
@@ -3630,7 +3356,7 @@
         <v>MHNL</v>
       </c>
       <c r="B115">
-        <v>246.4346482358764</v>
+        <v>243.20511967463074</v>
       </c>
       <c r="C115">
         <v>192</v>
@@ -3648,16 +3374,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="b">
-        <v>1</v>
-      </c>
-      <c r="I115">
-        <v>285</v>
-      </c>
-      <c r="J115" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K115">
-        <v>242.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3665,7 +3382,7 @@
         <v>SSHL</v>
       </c>
       <c r="B116">
-        <v>168.70029975280545</v>
+        <v>164.50584842187973</v>
       </c>
       <c r="C116">
         <v>128</v>
@@ -3683,16 +3400,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="b">
-        <v>1</v>
-      </c>
-      <c r="I116">
-        <v>190</v>
-      </c>
-      <c r="J116" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K116">
-        <v>160.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3700,7 +3408,7 @@
         <v>NYADI</v>
       </c>
       <c r="B117">
-        <v>356.11356808395743</v>
+        <v>342.72926975438054</v>
       </c>
       <c r="C117">
         <v>232</v>
@@ -3726,13 +3434,13 @@
         <v>GHL</v>
       </c>
       <c r="B118">
-        <v>218.0714401927995</v>
+        <v>221.8490938958488</v>
       </c>
       <c r="C118">
         <v>183.6216</v>
       </c>
       <c r="D118">
-        <v>112</v>
+        <v>145.75977044210785</v>
       </c>
       <c r="E118">
         <v>283</v>
@@ -3752,7 +3460,7 @@
         <v>GLH</v>
       </c>
       <c r="B119">
-        <v>241.9063081232254</v>
+        <v>235.3394051153673</v>
       </c>
       <c r="C119">
         <v>160</v>
@@ -3778,7 +3486,7 @@
         <v>RADHI</v>
       </c>
       <c r="B120">
-        <v>561.3006787396937</v>
+        <v>448.6421963339663</v>
       </c>
       <c r="C120">
         <v>208</v>
@@ -3804,7 +3512,7 @@
         <v>HURJA</v>
       </c>
       <c r="B121">
-        <v>222.859980234191</v>
+        <v>216.57911649218119</v>
       </c>
       <c r="C121">
         <v>171.2</v>
@@ -3822,16 +3530,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="b">
-        <v>1</v>
-      </c>
-      <c r="I121">
-        <v>257</v>
-      </c>
-      <c r="J121" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K121">
-        <v>218.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3839,7 +3538,7 @@
         <v>AKJCL</v>
       </c>
       <c r="B122">
-        <v>200.9116692018261</v>
+        <v>199.7869558461796</v>
       </c>
       <c r="C122">
         <v>152</v>
@@ -3865,7 +3564,7 @@
         <v>LEC</v>
       </c>
       <c r="B123">
-        <v>209.41978215652446</v>
+        <v>199.87285896382562</v>
       </c>
       <c r="C123">
         <v>152</v>
@@ -3891,7 +3590,7 @@
         <v>UPCL</v>
       </c>
       <c r="B124">
-        <v>353.46725207090367</v>
+        <v>291.0608765672135</v>
       </c>
       <c r="C124">
         <v>160</v>
@@ -3917,10 +3616,10 @@
         <v>RIDI</v>
       </c>
       <c r="B125">
-        <v>231.48553226529074</v>
+        <v>230.95960698052053</v>
       </c>
       <c r="C125">
-        <v>169.94110480498733</v>
+        <v>166.57100810241423</v>
       </c>
       <c r="D125">
         <v>112</v>
@@ -3943,13 +3642,13 @@
         <v>NHPC</v>
       </c>
       <c r="B126">
-        <v>208.96549122786547</v>
+        <v>211.46869779565458</v>
       </c>
       <c r="C126">
         <v>175.98319231991923</v>
       </c>
       <c r="D126">
-        <v>112</v>
+        <v>143.60088719116192</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3969,7 +3668,7 @@
         <v>MEN</v>
       </c>
       <c r="B127">
-        <v>580.9634954506929</v>
+        <v>579.6440908571137</v>
       </c>
       <c r="C127">
         <v>436</v>
@@ -3998,10 +3697,10 @@
         <v>195</v>
       </c>
       <c r="C128">
-        <v>164.25806718178285</v>
+        <v>164.11626073340676</v>
       </c>
       <c r="D128">
-        <v>109.2</v>
+        <v>129.02100368545157</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4021,7 +3720,7 @@
         <v>SHEL</v>
       </c>
       <c r="B129">
-        <v>257.81016527505807</v>
+        <v>257.60012022570464</v>
       </c>
       <c r="C129">
         <v>180</v>
@@ -4047,7 +3746,7 @@
         <v>BPCL</v>
       </c>
       <c r="B130">
-        <v>785.7326527737922</v>
+        <v>512.1344</v>
       </c>
       <c r="C130">
         <v>300.37949836496045</v>
@@ -4076,7 +3775,7 @@
         <v>305.53395596331023</v>
       </c>
       <c r="C131">
-        <v>260.91436396465946</v>
+        <v>260.72050451516816</v>
       </c>
       <c r="D131">
         <v>168</v>
@@ -4091,16 +3790,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="b">
-        <v>1</v>
-      </c>
-      <c r="I131">
-        <v>335</v>
-      </c>
-      <c r="J131" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K131">
-        <v>300.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4108,7 +3798,7 @@
         <v>NGPL</v>
       </c>
       <c r="B132">
-        <v>353.34295255724993</v>
+        <v>325.68339912301195</v>
       </c>
       <c r="C132">
         <v>203.2</v>
@@ -4126,16 +3816,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="b">
-        <v>1</v>
-      </c>
-      <c r="I132">
-        <v>200.78</v>
-      </c>
-      <c r="J132" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K132">
-        <v>340.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -4143,10 +3824,10 @@
         <v>SHPC</v>
       </c>
       <c r="B133">
-        <v>519.7670655459881</v>
+        <v>506.1439802494088</v>
       </c>
       <c r="C133">
-        <v>352</v>
+        <v>321.12178490265404</v>
       </c>
       <c r="D133">
         <v>246.4</v>
@@ -4169,7 +3850,7 @@
         <v>SAHAS</v>
       </c>
       <c r="B134">
-        <v>545.9895458813357</v>
+        <v>521.065508430828</v>
       </c>
       <c r="C134">
         <v>369.6</v>
@@ -4195,10 +3876,10 @@
         <v>AHPC</v>
       </c>
       <c r="B135">
-        <v>262.4629600126049</v>
+        <v>258.57739327544294</v>
       </c>
       <c r="C135">
-        <v>201.63</v>
+        <v>201.8016</v>
       </c>
       <c r="D135">
         <v>134.4</v>
@@ -4221,10 +3902,10 @@
         <v>AKPL</v>
       </c>
       <c r="B136">
-        <v>234.9298147329126</v>
+        <v>198.49835399744907</v>
       </c>
       <c r="C136">
-        <v>168.30148812127038</v>
+        <v>162.2504726548861</v>
       </c>
       <c r="D136">
         <v>125.44</v>
@@ -4239,16 +3920,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="b">
-        <v>1</v>
-      </c>
-      <c r="I136">
-        <v>235</v>
-      </c>
-      <c r="J136" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K136">
-        <v>199.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -4256,7 +3928,7 @@
         <v>MBJC</v>
       </c>
       <c r="B137">
-        <v>313.4396828963335</v>
+        <v>313.9578804984426</v>
       </c>
       <c r="C137">
         <v>264</v>
@@ -4274,16 +3946,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="b">
-        <v>1</v>
-      </c>
-      <c r="I137">
-        <v>328</v>
-      </c>
-      <c r="J137" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K137">
-        <v>278.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4291,10 +3954,10 @@
         <v>API</v>
       </c>
       <c r="B138">
-        <v>275.8972163697553</v>
+        <v>273.4143299581017</v>
       </c>
       <c r="C138">
-        <v>182.4</v>
+        <v>204.938267121966</v>
       </c>
       <c r="D138">
         <v>127.68</v>
@@ -4320,7 +3983,7 @@
         <v>368.3330169083814</v>
       </c>
       <c r="C139">
-        <v>265.4453919402269</v>
+        <v>264.655124217218</v>
       </c>
       <c r="D139">
         <v>196</v>
@@ -4346,7 +4009,7 @@
         <v>500</v>
       </c>
       <c r="C140">
-        <v>434.0087811044336</v>
+        <v>433.07376853176726</v>
       </c>
       <c r="D140">
         <v>280</v>
@@ -4372,7 +4035,7 @@
         <v>200</v>
       </c>
       <c r="C141">
-        <v>158.1985734371252</v>
+        <v>158.25643241820117</v>
       </c>
       <c r="D141">
         <v>112</v>
@@ -4387,16 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="b">
-        <v>1</v>
-      </c>
-      <c r="I141">
-        <v>199.9</v>
-      </c>
-      <c r="J141" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K141">
-        <v>190.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -4404,7 +4058,7 @@
         <v>RBCL</v>
       </c>
       <c r="B142">
-        <v>13125.126017805915</v>
+        <v>13137.247637414903</v>
       </c>
       <c r="C142">
         <v>10400</v>
@@ -4433,7 +4087,7 @@
         <v>936</v>
       </c>
       <c r="C143">
-        <v>777.9602800191753</v>
+        <v>760.3560243530839</v>
       </c>
       <c r="D143">
         <v>524.16</v>
@@ -4462,7 +4116,7 @@
         <v>757.392248363732</v>
       </c>
       <c r="D144">
-        <v>580.7597366877586</v>
+        <v>605.5607160704545</v>
       </c>
       <c r="E144">
         <v>1160</v>
@@ -4485,7 +4139,7 @@
         <v>700</v>
       </c>
       <c r="C145">
-        <v>541.6031765266507</v>
+        <v>538.9053923403416</v>
       </c>
       <c r="D145">
         <v>392</v>
@@ -4511,7 +4165,7 @@
         <v>773.2375069149816</v>
       </c>
       <c r="C146">
-        <v>685.4023166084321</v>
+        <v>650.9265597946998</v>
       </c>
       <c r="D146">
         <v>425.6</v>
@@ -4534,10 +4188,10 @@
         <v>UAIL</v>
       </c>
       <c r="B147">
-        <v>553.3059042203563</v>
+        <v>558.5584924964044</v>
       </c>
       <c r="C147">
-        <v>496</v>
+        <v>510.5</v>
       </c>
       <c r="D147">
         <v>347.20000000000005</v>
@@ -4560,7 +4214,7 @@
         <v>HEI</v>
       </c>
       <c r="B148">
-        <v>576.8110568340094</v>
+        <v>575.3524292553097</v>
       </c>
       <c r="C148">
         <v>496</v>
@@ -4578,16 +4232,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="b">
-        <v>1</v>
-      </c>
-      <c r="I148">
-        <v>566</v>
-      </c>
-      <c r="J148" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K148">
-        <v>481.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4595,10 +4240,10 @@
         <v>NLG</v>
       </c>
       <c r="B149">
-        <v>811.853149718722</v>
+        <v>850</v>
       </c>
       <c r="C149">
-        <v>749.8632587340362</v>
+        <v>758.7831658482652</v>
       </c>
       <c r="D149">
         <v>476</v>
@@ -4621,7 +4266,7 @@
         <v>SALICO</v>
       </c>
       <c r="B150">
-        <v>697.4329266665889</v>
+        <v>701.8319940273059</v>
       </c>
       <c r="C150">
         <v>544</v>
@@ -4647,7 +4292,7 @@
         <v>SPIL</v>
       </c>
       <c r="B151">
-        <v>802.2578268139994</v>
+        <v>802.8038121989662</v>
       </c>
       <c r="C151">
         <v>656</v>
@@ -4673,7 +4318,7 @@
         <v>SICL</v>
       </c>
       <c r="B152">
-        <v>733.9148011829889</v>
+        <v>736.4131498750355</v>
       </c>
       <c r="C152">
         <v>592</v>
@@ -4699,7 +4344,7 @@
         <v>IGI</v>
       </c>
       <c r="B153">
-        <v>559.6640089725342</v>
+        <v>566.4263863263146</v>
       </c>
       <c r="C153">
         <v>456</v>
@@ -4725,7 +4370,7 @@
         <v>NFS</v>
       </c>
       <c r="B154">
-        <v>665.628404974</v>
+        <v>518.1365364420991</v>
       </c>
       <c r="C154">
         <v>400</v>
@@ -4743,16 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="b">
-        <v>1</v>
-      </c>
-      <c r="I154">
-        <v>694</v>
-      </c>
-      <c r="J154" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K154">
-        <v>537.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -4760,10 +4396,10 @@
         <v>MPFL</v>
       </c>
       <c r="B155">
-        <v>555.4466517850489</v>
+        <v>600</v>
       </c>
       <c r="C155">
-        <v>440.64510309030976</v>
+        <v>441.6325574778943</v>
       </c>
       <c r="D155">
         <v>336</v>
@@ -4778,16 +4414,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
-      </c>
-      <c r="I155">
-        <v>640</v>
-      </c>
-      <c r="J155" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K155">
-        <v>544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -4798,10 +4425,10 @@
         <v>500</v>
       </c>
       <c r="C156">
-        <v>404.45600474050764</v>
+        <v>444.0594826533521</v>
       </c>
       <c r="D156">
-        <v>346.62677234344284</v>
+        <v>344.84063761227395</v>
       </c>
       <c r="E156">
         <v>1200</v>
@@ -4821,10 +4448,10 @@
         <v>JFL</v>
       </c>
       <c r="B157">
-        <v>472.0305452511782</v>
+        <v>500</v>
       </c>
       <c r="C157">
-        <v>423.9</v>
+        <v>438.4316114813071</v>
       </c>
       <c r="D157">
         <v>280</v>
@@ -4839,16 +4466,7 @@
         <v>0</v>
       </c>
       <c r="H157" t="b">
-        <v>1</v>
-      </c>
-      <c r="I157">
-        <v>490</v>
-      </c>
-      <c r="J157" t="str">
-        <v>2025-07-25</v>
-      </c>
-      <c r="K157">
-        <v>397.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -4859,7 +4477,7 @@
         <v>570</v>
       </c>
       <c r="C158">
-        <v>466.00031891923817</v>
+        <v>425.5500680942345</v>
       </c>
       <c r="D158">
         <v>319.20000000000005</v>
@@ -4874,16 +4492,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="b">
-        <v>1</v>
-      </c>
-      <c r="I158">
-        <v>484</v>
-      </c>
-      <c r="J158" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K158">
-        <v>411.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -4894,10 +4503,10 @@
         <v>520</v>
       </c>
       <c r="C159">
-        <v>412.2743002017796</v>
+        <v>380.3724852240444</v>
       </c>
       <c r="D159">
-        <v>345.52649001551896</v>
+        <v>343.39526943401364</v>
       </c>
       <c r="E159">
         <v>870</v>
@@ -4917,10 +4526,10 @@
         <v>GUFL</v>
       </c>
       <c r="B160">
-        <v>541.9148730134851</v>
+        <v>532.6924454411777</v>
       </c>
       <c r="C160">
-        <v>440</v>
+        <v>480.3447209765204</v>
       </c>
       <c r="D160">
         <v>308</v>
@@ -4943,7 +4552,7 @@
         <v>PFL</v>
       </c>
       <c r="B161">
-        <v>337.73503995713867</v>
+        <v>362.96049536536214</v>
       </c>
       <c r="C161">
         <v>264</v>
@@ -4972,7 +4581,7 @@
         <v>500</v>
       </c>
       <c r="C162">
-        <v>427.8618578032756</v>
+        <v>387.499403176546</v>
       </c>
       <c r="D162">
         <v>280</v>
@@ -4998,7 +4607,7 @@
         <v>650</v>
       </c>
       <c r="C163">
-        <v>512.4356932754627</v>
+        <v>455.37811256246516</v>
       </c>
       <c r="D163">
         <v>364</v>
@@ -5021,10 +4630,10 @@
         <v>GMFIL</v>
       </c>
       <c r="B164">
-        <v>444.7858141377678</v>
+        <v>422.4302217218624</v>
       </c>
       <c r="C164">
-        <v>387.95470238491527</v>
+        <v>387.84549822192247</v>
       </c>
       <c r="D164">
         <v>246.4</v>
@@ -5039,16 +4648,7 @@
         <v>0</v>
       </c>
       <c r="H164" t="b">
-        <v>1</v>
-      </c>
-      <c r="I164">
-        <v>503.9</v>
-      </c>
-      <c r="J164" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K164">
-        <v>428.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -5056,7 +4656,7 @@
         <v>SIFC</v>
       </c>
       <c r="B165">
-        <v>475.61444866489285</v>
+        <v>464.75413431783204</v>
       </c>
       <c r="C165">
         <v>362.93920890896163</v>
@@ -5074,16 +4674,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165">
-        <v>529</v>
-      </c>
-      <c r="J165" t="str">
-        <v>2025-07-14</v>
-      </c>
-      <c r="K165">
-        <v>449.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -5094,7 +4685,7 @@
         <v>500</v>
       </c>
       <c r="C166">
-        <v>444.14221142092396</v>
+        <v>397.00534106008024</v>
       </c>
       <c r="D166">
         <v>280</v>
@@ -5109,16 +4700,7 @@
         <v>0</v>
       </c>
       <c r="H166" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166">
-        <v>490</v>
-      </c>
-      <c r="J166" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K166">
-        <v>416.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -5129,7 +4711,7 @@
         <v>620</v>
       </c>
       <c r="C167">
-        <v>527.1915739006142</v>
+        <v>527.5589558414157</v>
       </c>
       <c r="D167">
         <v>347.20000000000005</v>
@@ -5155,7 +4737,7 @@
         <v>610</v>
       </c>
       <c r="C168">
-        <v>511.6963235013855</v>
+        <v>512.2225178750673</v>
       </c>
       <c r="D168">
         <v>341.6</v>
@@ -5178,10 +4760,10 @@
         <v>NWCL</v>
       </c>
       <c r="B169">
-        <v>895.0287447426648</v>
+        <v>896.3135769994205</v>
       </c>
       <c r="C169">
-        <v>719.558285478251</v>
+        <v>731.0780066677493</v>
       </c>
       <c r="D169">
         <v>532</v>
@@ -5204,10 +4786,10 @@
         <v>MKCL</v>
       </c>
       <c r="B170">
-        <v>1470.1984877531431</v>
+        <v>1384.2846195873826</v>
       </c>
       <c r="C170">
-        <v>1058.1578</v>
+        <v>1053.0958266271384</v>
       </c>
       <c r="D170">
         <v>672</v>
@@ -5230,7 +4812,7 @@
         <v>NTC</v>
       </c>
       <c r="B171">
-        <v>871.103945058989</v>
+        <v>874.9441294458046</v>
       </c>
       <c r="C171">
         <v>720</v>
@@ -5256,7 +4838,7 @@
         <v>NRIC</v>
       </c>
       <c r="B172">
-        <v>1258.2134043261062</v>
+        <v>1052.5497</v>
       </c>
       <c r="C172">
         <v>640</v>
@@ -5282,7 +4864,7 @@
         <v>HRL</v>
       </c>
       <c r="B173">
-        <v>867.4260980725301</v>
+        <v>863.926224888338</v>
       </c>
       <c r="C173">
         <v>624</v>
@@ -5308,7 +4890,7 @@
         <v>NRM</v>
       </c>
       <c r="B174">
-        <v>420.8095289503365</v>
+        <v>412.3107255037585</v>
       </c>
       <c r="C174">
         <v>336</v>
@@ -5334,7 +4916,7 @@
         <v>SHL</v>
       </c>
       <c r="B175">
-        <v>488.3256079454793</v>
+        <v>484.3801727964517</v>
       </c>
       <c r="C175">
         <v>368</v>
@@ -5360,7 +4942,7 @@
         <v>CGH</v>
       </c>
       <c r="B176">
-        <v>891.4660576674783</v>
+        <v>892.1233483744912</v>
       </c>
       <c r="C176">
         <v>696</v>
@@ -5389,7 +4971,7 @@
         <v>1020</v>
       </c>
       <c r="C177">
-        <v>754.3704025766798</v>
+        <v>749.6930826266805</v>
       </c>
       <c r="D177">
         <v>571.2</v>
@@ -5415,7 +4997,7 @@
         <v>845</v>
       </c>
       <c r="C178">
-        <v>754.7646274057751</v>
+        <v>744.8529362396547</v>
       </c>
       <c r="D178">
         <v>473.20000000000005</v>
@@ -5441,10 +5023,10 @@
         <v>860</v>
       </c>
       <c r="C179">
-        <v>809.9886814826644</v>
+        <v>732.9</v>
       </c>
       <c r="D179">
-        <v>583.5232936081426</v>
+        <v>585.1504628212789</v>
       </c>
       <c r="E179">
         <v>1200</v>
@@ -5464,7 +5046,7 @@
         <v>KDL</v>
       </c>
       <c r="B180">
-        <v>1061.4170787354028</v>
+        <v>1065.3944398126714</v>
       </c>
       <c r="C180">
         <v>778.0711837659542</v>
@@ -5490,7 +5072,7 @@
         <v>BNL</v>
       </c>
       <c r="B181">
-        <v>15975.63594786185</v>
+        <v>16314.342817201767</v>
       </c>
       <c r="C181">
         <v>12000</v>
@@ -5516,10 +5098,10 @@
         <v>BNT</v>
       </c>
       <c r="B182">
-        <v>13098.495723192724</v>
+        <v>13315.416228239274</v>
       </c>
       <c r="C182">
-        <v>10400</v>
+        <v>11302.343277131005</v>
       </c>
       <c r="D182">
         <v>7280</v>
@@ -5542,7 +5124,7 @@
         <v>GCIL</v>
       </c>
       <c r="B183">
-        <v>481.08107219616863</v>
+        <v>479.83545821992044</v>
       </c>
       <c r="C183">
         <v>400</v>
@@ -5568,7 +5150,7 @@
         <v>HDL</v>
       </c>
       <c r="B184">
-        <v>1237.4544716130576</v>
+        <v>1245.2215175989127</v>
       </c>
       <c r="C184">
         <v>912</v>
@@ -5594,7 +5176,7 @@
         <v>SARBTM</v>
       </c>
       <c r="B185">
-        <v>796.7119946443875</v>
+        <v>785.0848315995177</v>
       </c>
       <c r="C185">
         <v>560</v>
@@ -5620,7 +5202,7 @@
         <v>SHIVM</v>
       </c>
       <c r="B186">
-        <v>537.2458528366623</v>
+        <v>529.5741588189978</v>
       </c>
       <c r="C186">
         <v>400</v>
@@ -5646,7 +5228,7 @@
         <v>SONA</v>
       </c>
       <c r="B187">
-        <v>449.6021181005955</v>
+        <v>449.0669287368145</v>
       </c>
       <c r="C187">
         <v>368</v>
@@ -5698,7 +5280,7 @@
         <v>UNL</v>
       </c>
       <c r="B189">
-        <v>45765.924048481436</v>
+        <v>45782.60990225871</v>
       </c>
       <c r="C189">
         <v>35200</v>
@@ -5724,10 +5306,10 @@
         <v>NABBC</v>
       </c>
       <c r="B190">
-        <v>1533.4167072783328</v>
+        <v>1392.0155460048393</v>
       </c>
       <c r="C190">
-        <v>504</v>
+        <v>580.3993004975208</v>
       </c>
       <c r="D190">
         <v>352.8</v>
@@ -5750,7 +5332,7 @@
         <v>CORBL</v>
       </c>
       <c r="B191">
-        <v>1542.1054130325233</v>
+        <v>1383.9036694965687</v>
       </c>
       <c r="C191">
         <v>496</v>
@@ -5776,7 +5358,7 @@
         <v>GRDBL</v>
       </c>
       <c r="B192">
-        <v>1063.0777685599792</v>
+        <v>631.5804860653035</v>
       </c>
       <c r="C192">
         <v>480</v>
@@ -5805,10 +5387,10 @@
         <v>942.282655316135</v>
       </c>
       <c r="C193">
-        <v>707.7743916312899</v>
+        <v>774.1682053986337</v>
       </c>
       <c r="D193">
-        <v>336</v>
+        <v>602.7921228405047</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -5828,10 +5410,10 @@
         <v>SAPDBL</v>
       </c>
       <c r="B194">
-        <v>711.5496019578479</v>
+        <v>781.5443194253178</v>
       </c>
       <c r="C194">
-        <v>416</v>
+        <v>512.6599713087112</v>
       </c>
       <c r="D194">
         <v>291.2</v>
@@ -5857,7 +5439,7 @@
         <v>540</v>
       </c>
       <c r="C195">
-        <v>485.0778063426365</v>
+        <v>480.3132162633641</v>
       </c>
       <c r="D195">
         <v>302.4</v>
@@ -5883,7 +5465,7 @@
         <v>515.9985125561868</v>
       </c>
       <c r="C196">
-        <v>476.5580858629322</v>
+        <v>379.9954450578663</v>
       </c>
       <c r="D196">
         <v>296.8</v>
@@ -5906,10 +5488,10 @@
         <v>KSBBL</v>
       </c>
       <c r="B197">
-        <v>456.98488573806793</v>
+        <v>420</v>
       </c>
       <c r="C197">
-        <v>367.95343622284753</v>
+        <v>369.41873865974713</v>
       </c>
       <c r="D197">
         <v>235.2</v>
@@ -5932,10 +5514,10 @@
         <v>SADBL</v>
       </c>
       <c r="B198">
-        <v>405.36652701495103</v>
+        <v>380</v>
       </c>
       <c r="C198">
-        <v>311.9726617809088</v>
+        <v>313.44985346990495</v>
       </c>
       <c r="D198">
         <v>212.8</v>
@@ -5958,10 +5540,10 @@
         <v>LBBL</v>
       </c>
       <c r="B199">
-        <v>460.8359153836781</v>
+        <v>430</v>
       </c>
       <c r="C199">
-        <v>375.29788950607605</v>
+        <v>375.53940771632267</v>
       </c>
       <c r="D199">
         <v>240.8</v>
@@ -5984,7 +5566,7 @@
         <v>MLBL</v>
       </c>
       <c r="B200">
-        <v>370.1065155845949</v>
+        <v>363.92197229363484</v>
       </c>
       <c r="C200">
         <v>288</v>
@@ -6010,10 +5592,10 @@
         <v>JBBL</v>
       </c>
       <c r="B201">
-        <v>331.90491615875277</v>
+        <v>340</v>
       </c>
       <c r="C201">
-        <v>294.5427142041104</v>
+        <v>306.0961286094715</v>
       </c>
       <c r="D201">
         <v>190.4</v>
@@ -6036,7 +5618,7 @@
         <v>SHINE</v>
       </c>
       <c r="B202">
-        <v>417.24079085506463</v>
+        <v>394.62081459806996</v>
       </c>
       <c r="C202">
         <v>320</v>
@@ -6062,7 +5644,7 @@
         <v>GBBL</v>
       </c>
       <c r="B203">
-        <v>396.82578499963415</v>
+        <v>395.7553868760798</v>
       </c>
       <c r="C203">
         <v>301.6</v>
@@ -6088,7 +5670,7 @@
         <v>MNBBL</v>
       </c>
       <c r="B204">
-        <v>380.63892992781143</v>
+        <v>381.4779028386007</v>
       </c>
       <c r="C204">
         <v>292.8</v>
@@ -6114,7 +5696,7 @@
         <v>SCB</v>
       </c>
       <c r="B205">
-        <v>619.0282559139303</v>
+        <v>617.2959114492792</v>
       </c>
       <c r="C205">
         <v>561.5577860391528</v>
@@ -6140,10 +5722,10 @@
         <v>SBI</v>
       </c>
       <c r="B206">
-        <v>404.5609975625714</v>
+        <v>400</v>
       </c>
       <c r="C206">
-        <v>298.08593710473826</v>
+        <v>298.26839986120467</v>
       </c>
       <c r="D206">
         <v>224</v>
@@ -6166,7 +5748,7 @@
         <v>EBL</v>
       </c>
       <c r="B207">
-        <v>607.0187288585403</v>
+        <v>609.5966340237651</v>
       </c>
       <c r="C207">
         <v>456</v>
@@ -6192,10 +5774,10 @@
         <v>MBL</v>
       </c>
       <c r="B208">
-        <v>231.98665775568494</v>
+        <v>210</v>
       </c>
       <c r="C208">
-        <v>172.46907273663663</v>
+        <v>174.291262549512</v>
       </c>
       <c r="D208">
         <v>117.6</v>
@@ -6218,10 +5800,10 @@
         <v>HBL</v>
       </c>
       <c r="B209">
-        <v>219.46610766248392</v>
+        <v>240</v>
       </c>
       <c r="C209">
-        <v>182.94962829082743</v>
+        <v>181.504325038667</v>
       </c>
       <c r="D209">
         <v>134.4</v>
@@ -6244,10 +5826,10 @@
         <v>SANIMA</v>
       </c>
       <c r="B210">
-        <v>315.5870777244624</v>
+        <v>278.3895145267891</v>
       </c>
       <c r="C210">
-        <v>250.81139431947796</v>
+        <v>251.0616053932958</v>
       </c>
       <c r="D210">
         <v>156.8</v>
@@ -6270,7 +5852,7 @@
         <v>ADBL</v>
       </c>
       <c r="B211">
-        <v>284.4179505512248</v>
+        <v>280.22568090350245</v>
       </c>
       <c r="C211">
         <v>249.91610070413122</v>
@@ -6296,10 +5878,10 @@
         <v>SBL</v>
       </c>
       <c r="B212">
-        <v>303.4548470127139</v>
+        <v>249.60735793276606</v>
       </c>
       <c r="C212">
-        <v>238.36411138851432</v>
+        <v>237.49850657315605</v>
       </c>
       <c r="D212">
         <v>145.6</v>
@@ -6325,7 +5907,7 @@
         <v>200</v>
       </c>
       <c r="C213">
-        <v>162.73914547817867</v>
+        <v>163.57370388338379</v>
       </c>
       <c r="D213">
         <v>112</v>
@@ -6348,7 +5930,7 @@
         <v>NBL</v>
       </c>
       <c r="B214">
-        <v>253.72357068839227</v>
+        <v>233.04483427141582</v>
       </c>
       <c r="C214">
         <v>184</v>
@@ -6374,7 +5956,7 @@
         <v>CZBIL</v>
       </c>
       <c r="B215">
-        <v>201.76317594984408</v>
+        <v>190.1872638448936</v>
       </c>
       <c r="C215">
         <v>167.388618418563</v>
@@ -6400,7 +5982,7 @@
         <v>NICA</v>
       </c>
       <c r="B216">
-        <v>366.0881229198647</v>
+        <v>366.29980906582676</v>
       </c>
       <c r="C216">
         <v>276</v>
@@ -6429,7 +6011,7 @@
         <v>232</v>
       </c>
       <c r="C217">
-        <v>197.2357871197211</v>
+        <v>196.14019876574</v>
       </c>
       <c r="D217">
         <v>129.92</v>
@@ -6455,7 +6037,7 @@
         <v>230</v>
       </c>
       <c r="C218">
-        <v>198.39352232843962</v>
+        <v>200.2053296554271</v>
       </c>
       <c r="D218">
         <v>128.8</v>
@@ -6478,7 +6060,7 @@
         <v>NABIL</v>
       </c>
       <c r="B219">
-        <v>423.441058630236</v>
+        <v>424.3238401574764</v>
       </c>
       <c r="C219">
         <v>336</v>
@@ -6504,10 +6086,10 @@
         <v>PRVU</v>
       </c>
       <c r="B220">
-        <v>184.13790000000003</v>
+        <v>200</v>
       </c>
       <c r="C220">
-        <v>146.5129765544172</v>
+        <v>150.40759113145833</v>
       </c>
       <c r="D220">
         <v>112</v>
@@ -6530,10 +6112,10 @@
         <v>LSL</v>
       </c>
       <c r="B221">
-        <v>222.4427121924689</v>
+        <v>200</v>
       </c>
       <c r="C221">
-        <v>158.81838969549838</v>
+        <v>158.16109660147626</v>
       </c>
       <c r="D221">
         <v>112</v>
@@ -6556,10 +6138,10 @@
         <v>KBL</v>
       </c>
       <c r="B222">
-        <v>172.712</v>
+        <v>172.2426</v>
       </c>
       <c r="C222">
-        <v>144.4876678522174</v>
+        <v>141.60024842499834</v>
       </c>
       <c r="D222">
         <v>100.80000000000001</v>
@@ -6585,7 +6167,7 @@
         <v>200</v>
       </c>
       <c r="C223">
-        <v>184.16995530515723</v>
+        <v>184.80050686440688</v>
       </c>
       <c r="D223">
         <v>112</v>
@@ -6608,7 +6190,7 @@
         <v>GMLI</v>
       </c>
       <c r="B224">
-        <v>1626.9338999999998</v>
+        <v>1626.70525</v>
       </c>
       <c r="C224">
         <v>800</v>
@@ -6634,7 +6216,7 @@
         <v>PMLI</v>
       </c>
       <c r="B225">
-        <v>493.15636500324933</v>
+        <v>491.362493698805</v>
       </c>
       <c r="C225">
         <v>400</v>
@@ -6663,7 +6245,7 @@
         <v>600</v>
       </c>
       <c r="C226">
-        <v>472.1060896016734</v>
+        <v>491.62552978351977</v>
       </c>
       <c r="D226">
         <v>336</v>
@@ -6678,16 +6260,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="b">
-        <v>1</v>
-      </c>
-      <c r="I226">
-        <v>480</v>
-      </c>
-      <c r="J226" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K226">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -6698,7 +6271,7 @@
         <v>600</v>
       </c>
       <c r="C227">
-        <v>464.38916430192614</v>
+        <v>459.7585368312643</v>
       </c>
       <c r="D227">
         <v>336</v>
@@ -6721,10 +6294,10 @@
         <v>RNLI</v>
       </c>
       <c r="B228">
-        <v>463.8131921951733</v>
+        <v>463.6475910333433</v>
       </c>
       <c r="C228">
-        <v>408</v>
+        <v>433.65708831555514</v>
       </c>
       <c r="D228">
         <v>285.6</v>
@@ -6747,7 +6320,7 @@
         <v>ILI</v>
       </c>
       <c r="B229">
-        <v>454.4898166850883</v>
+        <v>455.5031406242807</v>
       </c>
       <c r="C229">
         <v>368</v>
@@ -6776,7 +6349,7 @@
         <v>1082.9308288310187</v>
       </c>
       <c r="C230">
-        <v>883.5454503546979</v>
+        <v>975</v>
       </c>
       <c r="D230">
         <v>560</v>
@@ -6802,7 +6375,7 @@
         <v>700</v>
       </c>
       <c r="C231">
-        <v>492.1587515942547</v>
+        <v>542.1</v>
       </c>
       <c r="D231">
         <v>392</v>
@@ -6825,7 +6398,7 @@
         <v>NLICL</v>
       </c>
       <c r="B232">
-        <v>585.154309716405</v>
+        <v>576.813252871162</v>
       </c>
       <c r="C232">
         <v>448</v>
@@ -6851,7 +6424,7 @@
         <v>SRLI</v>
       </c>
       <c r="B233">
-        <v>425.11961833297966</v>
+        <v>426.7685471049732</v>
       </c>
       <c r="C233">
         <v>288</v>
@@ -6869,16 +6442,7 @@
         <v>0</v>
       </c>
       <c r="H233" t="b">
-        <v>1</v>
-      </c>
-      <c r="I233">
-        <v>406</v>
-      </c>
-      <c r="J233" t="str">
-        <v>2025-06-19</v>
-      </c>
-      <c r="K233">
-        <v>345.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -6886,7 +6450,7 @@
         <v>SJLIC</v>
       </c>
       <c r="B234">
-        <v>426.2879305078672</v>
+        <v>424.65609445283457</v>
       </c>
       <c r="C234">
         <v>320</v>
@@ -6915,7 +6479,7 @@
         <v>690</v>
       </c>
       <c r="C235">
-        <v>598.2645897262158</v>
+        <v>597.8315469265785</v>
       </c>
       <c r="D235">
         <v>386.4</v>
@@ -6938,7 +6502,7 @@
         <v>HLI</v>
       </c>
       <c r="B236">
-        <v>391.46769251676835</v>
+        <v>390.0773921207653</v>
       </c>
       <c r="C236">
         <v>312</v>
@@ -6967,7 +6531,7 @@
         <v>1039.7272135496446</v>
       </c>
       <c r="C237">
-        <v>893.651760452362</v>
+        <v>888.7549331801875</v>
       </c>
       <c r="D237">
         <v>560</v>
@@ -6990,10 +6554,10 @@
         <v>ENL</v>
       </c>
       <c r="B238">
-        <v>1062.5781535148476</v>
+        <v>1066.4561397296002</v>
       </c>
       <c r="C238">
-        <v>840</v>
+        <v>856.0851955461036</v>
       </c>
       <c r="D238">
         <v>588</v>
@@ -7016,7 +6580,7 @@
         <v>CHDC</v>
       </c>
       <c r="B239">
-        <v>2091.4393677349585</v>
+        <v>1910.2471690562281</v>
       </c>
       <c r="C239">
         <v>960</v>
@@ -7042,7 +6606,7 @@
         <v>NRN</v>
       </c>
       <c r="B240">
-        <v>1712.9325013668079</v>
+        <v>1197.4550708449967</v>
       </c>
       <c r="C240">
         <v>680</v>
@@ -7068,7 +6632,7 @@
         <v>CIT</v>
       </c>
       <c r="B241">
-        <v>1934.0066048773556</v>
+        <v>1932.1990300059142</v>
       </c>
       <c r="C241">
         <v>1576</v>
@@ -7094,10 +6658,10 @@
         <v>HIDCL</v>
       </c>
       <c r="B242">
-        <v>258.6740255093663</v>
+        <v>256.27534146265936</v>
       </c>
       <c r="C242">
-        <v>188</v>
+        <v>162.20870074334456</v>
       </c>
       <c r="D242">
         <v>131.6</v>
@@ -7120,10 +6684,10 @@
         <v>NIFRA</v>
       </c>
       <c r="B243">
-        <v>261.5752074654113</v>
+        <v>261.97725957684384</v>
       </c>
       <c r="C243">
-        <v>197.62473858523174</v>
+        <v>198.57023999605818</v>
       </c>
       <c r="D243">
         <v>134.4</v>
@@ -7146,7 +6710,7 @@
         <v>CREST</v>
       </c>
       <c r="B244">
-        <v>1343.0779343315235</v>
+        <v>1343.0333333333333</v>
       </c>
       <c r="C244">
         <v>1000</v>
@@ -7175,10 +6739,10 @@
         <v>1000</v>
       </c>
       <c r="C245">
-        <v>1530.3193419650645</v>
+        <v>1530.85433858147</v>
       </c>
       <c r="D245">
-        <v>1500</v>
+        <v>1338.4</v>
       </c>
       <c r="E245">
         <v>2500</v>
@@ -7198,7 +6762,7 @@
         <v>OMPL</v>
       </c>
       <c r="B246">
-        <v>1308.806082903429</v>
+        <v>1339.0000000000002</v>
       </c>
       <c r="C246">
         <v>1500</v>
@@ -7224,10 +6788,10 @@
         <v>PURE</v>
       </c>
       <c r="B247">
-        <v>600</v>
+        <v>845.409891719016</v>
       </c>
       <c r="C247">
-        <v>400</v>
+        <v>505.10917183225274</v>
       </c>
       <c r="D247">
         <v>300</v>
@@ -7245,465 +6809,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>TTL</v>
-      </c>
-      <c r="B248">
-        <v>400</v>
-      </c>
-      <c r="C248">
-        <v>500</v>
-      </c>
-      <c r="D248">
-        <v>600</v>
-      </c>
-      <c r="E248">
-        <v>700</v>
-      </c>
-      <c r="F248" t="str">
-        <v>OTHERS</v>
-      </c>
-      <c r="G248" t="b">
-        <v>0</v>
-      </c>
-      <c r="H248" t="b">
-        <v>0</v>
-      </c>
-      <c r="L248" t="str">
-        <v>2025-07-20T10:25:13.270Z</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>SANVI</v>
-      </c>
-      <c r="B249">
-        <v>300</v>
-      </c>
-      <c r="C249">
-        <v>400</v>
-      </c>
-      <c r="D249">
-        <v>500</v>
-      </c>
-      <c r="E249">
-        <v>900</v>
-      </c>
-      <c r="F249" t="str">
-        <v>HYDROPOWER</v>
-      </c>
-      <c r="G249" t="b">
-        <v>0</v>
-      </c>
-      <c r="H249" t="b">
-        <v>0</v>
-      </c>
-      <c r="L249" t="str">
-        <v>2025-07-20T10:25:38.664Z</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L249"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K247"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C111"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>symbol</v>
       </c>
       <c r="B1" t="str">
-        <v>type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>rightsPercentage</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PURE</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>OMPL</v>
-      </c>
-      <c r="B3" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>CREST</v>
-      </c>
-      <c r="B4" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>NMIC</v>
-      </c>
-      <c r="B5" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>GMLI</v>
-      </c>
-      <c r="B6" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>NWCL</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>MMKJL</v>
-      </c>
-      <c r="B8" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CKHL</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>VLUCL</v>
-      </c>
-      <c r="B10" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>CHDC</v>
-      </c>
-      <c r="B11" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>NICLBSL</v>
-      </c>
-      <c r="B12" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>PPL</v>
-      </c>
-      <c r="B13" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>BARUN</v>
-      </c>
-      <c r="B14" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>ALICL</v>
-      </c>
-      <c r="B15" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>NABBC</v>
-      </c>
-      <c r="B16" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>RHGCL</v>
-      </c>
-      <c r="B17" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>TPC</v>
-      </c>
-      <c r="B18" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>CHL</v>
-      </c>
-      <c r="B19" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>SNLI</v>
-      </c>
-      <c r="B20" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>DORDI</v>
-      </c>
-      <c r="B21" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>NIL</v>
-      </c>
-      <c r="B22" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>BHL</v>
-      </c>
-      <c r="B23" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>LEC</v>
-      </c>
-      <c r="B24" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>LICN</v>
-      </c>
-      <c r="B25" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>NLG</v>
-      </c>
-      <c r="B26" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>HURJA</v>
-      </c>
-      <c r="B27" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>RIDI</v>
-      </c>
-      <c r="B28" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>GHL</v>
-      </c>
-      <c r="B29" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>MPFL</v>
-      </c>
-      <c r="B30" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>JOSHI</v>
-      </c>
-      <c r="B31" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>TTL</v>
-      </c>
-      <c r="B32" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>SANVI</v>
-      </c>
-      <c r="B33" t="str">
-        <v>ipo</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>RFPL</v>
-      </c>
-      <c r="B34" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>SSHL</v>
-      </c>
-      <c r="B35" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>CITY</v>
-      </c>
-      <c r="B36" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>KKHC</v>
-      </c>
-      <c r="B37" t="str">
-        <v>rights</v>
-      </c>
-      <c r="C37">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C87"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>symbol</v>
-      </c>
-      <c r="B1" t="str">
         <v>supportType</v>
       </c>
       <c r="C1" t="str">
@@ -8526,35 +7647,35 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>NADEP</v>
+        <v>USHEC</v>
       </c>
       <c r="B76" t="str">
         <v>support1</v>
       </c>
       <c r="C76" t="str">
-        <v>2025-07-20T10:19:35.208Z</v>
+        <v>2025-08-10T17:34:29.355Z</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HHL</v>
+        <v>KKHC</v>
       </c>
       <c r="B77" t="str">
-        <v>support1</v>
+        <v>support2</v>
       </c>
       <c r="C77" t="str">
-        <v>2025-07-20T10:19:35.209Z</v>
+        <v>2025-08-10T17:34:29.355Z</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>NLG</v>
+        <v>NYADI</v>
       </c>
       <c r="B78" t="str">
         <v>support1</v>
       </c>
       <c r="C78" t="str">
-        <v>2025-07-20T10:19:35.209Z</v>
+        <v>2025-08-10T17:34:29.355Z</v>
       </c>
     </row>
     <row r="79">
@@ -8565,100 +7686,364 @@
         <v>support1</v>
       </c>
       <c r="C79" t="str">
-        <v>2025-07-20T10:19:35.209Z</v>
+        <v>2025-08-10T17:34:29.356Z</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HBL</v>
+        <v>PROFL</v>
       </c>
       <c r="B80" t="str">
         <v>support1</v>
       </c>
       <c r="C80" t="str">
-        <v>2025-07-20T10:19:35.209Z</v>
+        <v>2025-08-10T17:34:29.356Z</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>TRH</v>
+        <v>NWCL</v>
       </c>
       <c r="B81" t="str">
         <v>support1</v>
       </c>
       <c r="C81" t="str">
-        <v>2025-07-25T02:17:57.727Z</v>
+        <v>2025-08-10T17:34:29.356Z</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SRLI</v>
+        <v>JOSHI</v>
       </c>
       <c r="B82" t="str">
         <v>support1</v>
       </c>
       <c r="C82" t="str">
-        <v>2025-07-25T02:17:57.728Z</v>
+        <v>2025-08-14T15:36:22.323Z</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>OMPL</v>
+        <v>SJCL</v>
       </c>
       <c r="B83" t="str">
         <v>support1</v>
       </c>
       <c r="C83" t="str">
-        <v>2025-07-29T15:23:55.610Z</v>
+        <v>2025-08-14T15:36:22.323Z</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>FOWAD</v>
+        <v>PRIN</v>
       </c>
       <c r="B84" t="str">
-        <v>support1</v>
+        <v>support2</v>
       </c>
       <c r="C84" t="str">
-        <v>2025-08-05T10:21:54.608Z</v>
+        <v>2025-08-14T15:36:22.323Z</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>CHL</v>
+        <v>SINDU</v>
       </c>
       <c r="B85" t="str">
         <v>support2</v>
       </c>
       <c r="C85" t="str">
-        <v>2025-08-05T10:21:54.610Z</v>
+        <v>2025-08-14T15:36:22.324Z</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>NWCL</v>
+        <v>JBBL</v>
       </c>
       <c r="B86" t="str">
         <v>support1</v>
       </c>
       <c r="C86" t="str">
-        <v>2025-08-05T10:21:54.612Z</v>
+        <v>2025-08-14T15:36:22.324Z</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ENL</v>
+        <v>RNLI</v>
       </c>
       <c r="B87" t="str">
         <v>support1</v>
       </c>
       <c r="C87" t="str">
-        <v>2025-08-05T10:21:54.613Z</v>
+        <v>2025-08-14T15:36:22.324Z</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>NMIC</v>
+      </c>
+      <c r="B88" t="str">
+        <v>support2</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2025-08-14T15:36:22.324Z</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>RSDC</v>
+      </c>
+      <c r="B89" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2025-08-30T13:04:41.383Z</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>SMHL</v>
+      </c>
+      <c r="B90" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2025-08-30T13:04:41.383Z</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>RHGCL</v>
+      </c>
+      <c r="B91" t="str">
+        <v>support2</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2025-08-30T13:04:41.384Z</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>AKJCL</v>
+      </c>
+      <c r="B92" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2025-08-30T13:04:41.384Z</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>HDHPC</v>
+      </c>
+      <c r="B93" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2025-08-30T13:04:41.384Z</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>SWBBL</v>
+      </c>
+      <c r="B94" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2025-09-02T04:43:44.579Z</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>SIKLES</v>
+      </c>
+      <c r="B95" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2025-09-02T04:43:44.579Z</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TVCL</v>
+      </c>
+      <c r="B96" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2025-09-02T04:43:44.579Z</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>KDL</v>
+      </c>
+      <c r="B97" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2025-09-02T04:43:44.579Z</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>UNLB</v>
+      </c>
+      <c r="B98" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2025-09-04T16:07:41.333Z</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>NMLBBL</v>
+      </c>
+      <c r="B99" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2025-09-04T16:07:41.334Z</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>RFPL</v>
+      </c>
+      <c r="B100" t="str">
+        <v>support2</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2025-09-04T16:07:41.334Z</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>MHNL</v>
+      </c>
+      <c r="B101" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2025-09-04T16:07:41.335Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>GHL</v>
+      </c>
+      <c r="B102" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2025-09-04T16:07:41.335Z</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>NICL</v>
+      </c>
+      <c r="B103" t="str">
+        <v>support3</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2025-09-04T16:07:41.335Z</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>NIL</v>
+      </c>
+      <c r="B104" t="str">
+        <v>support2</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2025-09-04T16:07:41.336Z</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>BNT</v>
+      </c>
+      <c r="B105" t="str">
+        <v>support2</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2025-09-04T16:07:41.336Z</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>GCIL</v>
+      </c>
+      <c r="B106" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2025-09-04T16:07:41.337Z</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>SAPDBL</v>
+      </c>
+      <c r="B107" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2025-09-04T16:07:41.337Z</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>PMLI</v>
+      </c>
+      <c r="B108" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2025-09-04T16:07:41.337Z</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>NLICL</v>
+      </c>
+      <c r="B109" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2025-09-04T16:07:41.338Z</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>HLI</v>
+      </c>
+      <c r="B110" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C110" t="str">
+        <v>2025-09-04T16:07:41.338Z</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>HATHY</v>
+      </c>
+      <c r="B111" t="str">
+        <v>support1</v>
+      </c>
+      <c r="C111" t="str">
+        <v>2025-09-04T16:07:41.338Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C111"/>
   </ignoredErrors>
 </worksheet>
 </file>